--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Escuela\CD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889C78A0-A6C0-4D0E-B7BE-50926C9DFACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08130C3-E3E5-4247-A0A5-DF17EC7DC445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B369BA19-151F-4125-A543-80395CDD3128}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="24">
   <si>
     <t>persona a persona</t>
   </si>
@@ -112,6 +112,12 @@
   </si>
   <si>
     <t>Panel solar</t>
+  </si>
+  <si>
+    <t>agencia en cuba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           2 años</t>
   </si>
 </sst>
 </file>
@@ -792,10 +798,36 @@
         <v>12</v>
       </c>
     </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="2">
+        <v>4500</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+    </row>
     <row r="1048576" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B1048576" s="2">
         <f>SUM(B1:B1048575)</f>
-        <v>71669.230769230766</v>
+        <v>76169.230769230766</v>
       </c>
     </row>
   </sheetData>
